--- a/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
+++ b/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J458"/>
+  <dimension ref="A1:J459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -18476,6 +18476,46 @@
         </is>
       </c>
     </row>
+    <row r="459">
+      <c r="A459" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B459" s="4" t="n"/>
+      <c r="C459" s="9" t="n">
+        <v>257553.9</v>
+      </c>
+      <c r="D459" s="10" t="n">
+        <v>-480.7</v>
+      </c>
+      <c r="E459" s="10" t="n">
+        <v>5424.3</v>
+      </c>
+      <c r="F459" s="11" t="n">
+        <v>0.045836</v>
+      </c>
+      <c r="G459" s="12" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="H459" s="12" t="inlineStr">
+        <is>
+          <t>Banco de México — SIE / Estado de cuenta semanal</t>
+        </is>
+      </c>
+      <c r="I459" s="12" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
+        </is>
+      </c>
+      <c r="J459" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>

--- a/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
+++ b/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J459"/>
+  <dimension ref="A1:J460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -18516,6 +18516,46 @@
         </is>
       </c>
     </row>
+    <row r="460">
+      <c r="A460" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B460" s="4" t="n"/>
+      <c r="C460" s="5" t="n">
+        <v>257238.2</v>
+      </c>
+      <c r="D460" s="6" t="n">
+        <v>-315.7</v>
+      </c>
+      <c r="E460" s="6" t="n">
+        <v>5108.6</v>
+      </c>
+      <c r="F460" s="7" t="n">
+        <v>0.043442</v>
+      </c>
+      <c r="G460" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="H460" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México — SIE / Estado de cuenta semanal</t>
+        </is>
+      </c>
+      <c r="I460" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
+        </is>
+      </c>
+      <c r="J460" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>

--- a/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
+++ b/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J460"/>
+  <dimension ref="A1:J461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -18556,6 +18556,46 @@
         </is>
       </c>
     </row>
+    <row r="461">
+      <c r="A461" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B461" s="4" t="n"/>
+      <c r="C461" s="9" t="n">
+        <v>256542.8</v>
+      </c>
+      <c r="D461" s="10" t="n">
+        <v>-695.4</v>
+      </c>
+      <c r="E461" s="10" t="n">
+        <v>4413.2</v>
+      </c>
+      <c r="F461" s="11" t="n">
+        <v>0.039343</v>
+      </c>
+      <c r="G461" s="12" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="H461" s="12" t="inlineStr">
+        <is>
+          <t>Banco de México — SIE / Estado de cuenta semanal</t>
+        </is>
+      </c>
+      <c r="I461" s="12" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
+        </is>
+      </c>
+      <c r="J461" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>

--- a/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
+++ b/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J461"/>
+  <dimension ref="A1:J462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -18596,6 +18596,46 @@
         </is>
       </c>
     </row>
+    <row r="462">
+      <c r="A462" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B462" s="4" t="n"/>
+      <c r="C462" s="5" t="n">
+        <v>256039.8</v>
+      </c>
+      <c r="D462" s="6" t="n">
+        <v>-503</v>
+      </c>
+      <c r="E462" s="6" t="n">
+        <v>3910.2</v>
+      </c>
+      <c r="F462" s="7" t="n">
+        <v>0.03353</v>
+      </c>
+      <c r="G462" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="H462" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México — SIE / Estado de cuenta semanal</t>
+        </is>
+      </c>
+      <c r="I462" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
+        </is>
+      </c>
+      <c r="J462" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>

--- a/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
+++ b/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J462"/>
+  <dimension ref="A1:J463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -18636,6 +18636,46 @@
         </is>
       </c>
     </row>
+    <row r="463">
+      <c r="A463" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B463" s="4" t="n"/>
+      <c r="C463" s="9" t="n">
+        <v>256344.4</v>
+      </c>
+      <c r="D463" s="10" t="n">
+        <v>304.6</v>
+      </c>
+      <c r="E463" s="10" t="n">
+        <v>4214.8</v>
+      </c>
+      <c r="F463" s="11" t="n">
+        <v>0.03261</v>
+      </c>
+      <c r="G463" s="12" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="H463" s="12" t="inlineStr">
+        <is>
+          <t>Banco de México — SIE / Estado de cuenta semanal</t>
+        </is>
+      </c>
+      <c r="I463" s="12" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
+        </is>
+      </c>
+      <c r="J463" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>

--- a/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
+++ b/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J463"/>
+  <dimension ref="A1:J464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -18676,6 +18676,46 @@
         </is>
       </c>
     </row>
+    <row r="464">
+      <c r="A464" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B464" s="4" t="n"/>
+      <c r="C464" s="5" t="n">
+        <v>257076.5</v>
+      </c>
+      <c r="D464" s="6" t="n">
+        <v>732.1</v>
+      </c>
+      <c r="E464" s="6" t="n">
+        <v>4946.9</v>
+      </c>
+      <c r="F464" s="7" t="n">
+        <v>0.02936</v>
+      </c>
+      <c r="G464" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="H464" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México — SIE / Estado de cuenta semanal</t>
+        </is>
+      </c>
+      <c r="I464" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
+        </is>
+      </c>
+      <c r="J464" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>

--- a/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
+++ b/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J464"/>
+  <dimension ref="A1:J465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -18716,6 +18716,46 @@
         </is>
       </c>
     </row>
+    <row r="465">
+      <c r="A465" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B465" s="4" t="n"/>
+      <c r="C465" s="9" t="n">
+        <v>257015.6</v>
+      </c>
+      <c r="D465" s="10" t="n">
+        <v>-60.9</v>
+      </c>
+      <c r="E465" s="10" t="n">
+        <v>4886</v>
+      </c>
+      <c r="F465" s="11" t="n">
+        <v>0.03078</v>
+      </c>
+      <c r="G465" s="12" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="H465" s="12" t="inlineStr">
+        <is>
+          <t>Banco de México — SIE / Estado de cuenta semanal</t>
+        </is>
+      </c>
+      <c r="I465" s="12" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
+        </is>
+      </c>
+      <c r="J465" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
